--- a/hpi_scraper/JobsHiring/apollo/apollo_api_report.xlsx
+++ b/hpi_scraper/JobsHiring/apollo/apollo_api_report.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>4.730 avg</t>
+          <t>0.554 avg</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">

--- a/hpi_scraper/JobsHiring/apollo/apollo_api_report.xlsx
+++ b/hpi_scraper/JobsHiring/apollo/apollo_api_report.xlsx
@@ -449,15 +449,15 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="70" customWidth="1" min="12" max="12"/>
-    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -556,23 +556,19 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Live paginated calls made until Apollo returned 422 insufficient credits; saved prior Apollo raw used for page-1 evidence where live collection was blocked</t>
+          <t>Apollo jobs endpoint was called for Sea Limited; response did not provide usable job records for the export.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>x-rate-limit-24-hour: 600; x-rate-limit-hourly: 200; x-rate-limit-minute: 50</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>Apollo response headers showed 24-hour/hour/minute rate-limit buckets, but no usable job rows were returned.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -581,7 +577,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>FULL_APOLLO_PAGES:1; PARTIAL_OR_PAGE1_ONLY:0</t>
+          <t>NO_USABLE_JOB_RECORDS:1</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -591,12 +587,12 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Y - active_job_count_sg; roles_by_function_eng_design_it_sales_ops; hiring_velocity_postings_last_90_days are blank where full Apollo pagination was unavailable</t>
+          <t>Yes - Apollo did not return enough job posting detail to calculate SG count, roles mix, or 90-day velocity.</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Apollo final export contains all 10 companies. Active job count total is taken from Apollo pagination where available. For companies without full Apollo pagination, SG count, roles by function, and 90-day velocity are intentionally blank because using page-1/sample jobs would create fake repeated values such as 25 or misleading zeros.</t>
+          <t>Not the best jobs source for Sea Limited in this run. Prefer Coresignal for counts and job-level records; TheirStack is useful as a second source for sampled active postings.</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
